--- a/data/carl_demo_requests.xlsx
+++ b/data/carl_demo_requests.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -904,10 +904,113 @@
           <t>Navale IT Zone</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
           <t>192.168.1.39</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-01-12 04:55:23 UTC</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>sujay jirapure</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>KGN Solar</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>sujay@gmail.com</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>BH</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>+973</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>+97398888899</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>50 Broughton Road</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>502 error test</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>192.168.1.54</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-01-12 09:23:03 UTC</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>sujay jirapure</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>KGN Solar</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>sujay@gmail.com</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>BH</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>+973</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>+97398888899</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>50 Broughton Road</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>testing 504 error in RMU</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>192.168.1.54</t>
         </is>
       </c>
     </row>
